--- a/appium-tests/reports/appium-test-report.xlsx
+++ b/appium-tests/reports/appium-test-report.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="332">
   <si>
     <t>Metric</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Run Date</t>
   </si>
   <si>
-    <t>23/7/2026, 9:52:28 am</t>
+    <t>23/7/2026, 10:19:16 am</t>
   </si>
   <si>
     <t>Total Test Cases</t>
@@ -48,7 +48,7 @@
     <t>Overall Pass Rate</t>
   </si>
   <si>
-    <t>97.67%</t>
+    <t>100.00%</t>
   </si>
   <si>
     <t>Total Duration (ms)</t>
@@ -57,7 +57,7 @@
     <t>Total Duration (s)</t>
   </si>
   <si>
-    <t>3.67</t>
+    <t>3.52</t>
   </si>
   <si>
     <t>Category Name</t>
@@ -78,15 +78,12 @@
     <t>Functional E2E</t>
   </si>
   <si>
-    <t>98.0%</t>
+    <t>100.0%</t>
   </si>
   <si>
     <t>UI UX Verification</t>
   </si>
   <si>
-    <t>97.0%</t>
-  </si>
-  <si>
     <t>Input Validation</t>
   </si>
   <si>
@@ -162,12 +159,6 @@
     <t>FUNC-016: Verify scenario details #16</t>
   </si>
   <si>
-    <t>FAIL</t>
-  </si>
-  <si>
-    <t>AssertionError: expected status 200 but received 500 for scenario #16</t>
-  </si>
-  <si>
     <t>FUNC-017: Verify scenario details #17</t>
   </si>
   <si>
@@ -225,9 +216,6 @@
     <t>FUNC-035: Verify scenario details #35</t>
   </si>
   <si>
-    <t>AssertionError: expected status 200 but received 500 for scenario #35</t>
-  </si>
-  <si>
     <t>FUNC-036: Verify scenario details #36</t>
   </si>
   <si>
@@ -429,9 +417,6 @@
     <t>UIUX-002: Verify scenario details #2</t>
   </si>
   <si>
-    <t>AssertionError: expected status 200 but received 500 for scenario #2</t>
-  </si>
-  <si>
     <t>UIUX-003: Verify scenario details #3</t>
   </si>
   <si>
@@ -540,9 +525,6 @@
     <t>UIUX-038: Verify scenario details #38</t>
   </si>
   <si>
-    <t>AssertionError: expected status 200 but received 500 for scenario #38</t>
-  </si>
-  <si>
     <t>UIUX-039: Verify scenario details #39</t>
   </si>
   <si>
@@ -705,9 +687,6 @@
     <t>UIUX-092: Verify scenario details #92</t>
   </si>
   <si>
-    <t>AssertionError: expected status 200 but received 500 for scenario #92</t>
-  </si>
-  <si>
     <t>UIUX-093: Verify scenario details #93</t>
   </si>
   <si>
@@ -804,9 +783,6 @@
     <t>VAL-024: Verify scenario details #24</t>
   </si>
   <si>
-    <t>AssertionError: expected status 200 but received 500 for scenario #24</t>
-  </si>
-  <si>
     <t>VAL-025: Verify scenario details #25</t>
   </si>
   <si>
@@ -886,9 +862,6 @@
   </si>
   <si>
     <t>VAL-051: Verify scenario details #51</t>
-  </si>
-  <si>
-    <t>AssertionError: expected status 200 but received 500 for scenario #51</t>
   </si>
   <si>
     <t>VAL-052: Verify scenario details #52</t>
@@ -1056,7 +1029,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1076,11 +1049,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="E8F5E9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEBEE"/>
       </patternFill>
     </fill>
   </fills>
@@ -1111,14 +1079,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1502,7 +1469,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="2">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1510,7 +1477,7 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1534,7 +1501,7 @@
         <v>12</v>
       </c>
       <c r="B9" s="2">
-        <v>3669</v>
+        <v>3519</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1588,10 +1555,10 @@
         <v>100</v>
       </c>
       <c r="C2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2" t="s">
         <v>21</v>
@@ -1605,27 +1572,27 @@
         <v>100</v>
       </c>
       <c r="C3" s="2">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D3" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B4">
         <v>100</v>
       </c>
       <c r="C4">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4" t="s">
         <v>21</v>
@@ -1653,22 +1620,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -1679,16 +1646,16 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1699,16 +1666,16 @@
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1719,16 +1686,16 @@
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1739,16 +1706,16 @@
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E5">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1759,16 +1726,16 @@
         <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1779,16 +1746,16 @@
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E7">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1799,16 +1766,16 @@
         <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1819,16 +1786,16 @@
         <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E9">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1839,16 +1806,16 @@
         <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1859,16 +1826,16 @@
         <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E11">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1879,16 +1846,16 @@
         <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E12">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1899,16 +1866,16 @@
         <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E13">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1919,16 +1886,16 @@
         <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E14">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1939,16 +1906,16 @@
         <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E15">
         <v>15</v>
       </c>
       <c r="F15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1959,16 +1926,16 @@
         <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E16">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1979,16 +1946,16 @@
         <v>20</v>
       </c>
       <c r="C17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="E17">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F17" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1999,16 +1966,16 @@
         <v>20</v>
       </c>
       <c r="C18" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E18">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -2019,16 +1986,16 @@
         <v>20</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E19">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -2039,16 +2006,16 @@
         <v>20</v>
       </c>
       <c r="C20" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E20">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="F20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -2059,16 +2026,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E21">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -2079,16 +2046,16 @@
         <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E22">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -2099,16 +2066,16 @@
         <v>20</v>
       </c>
       <c r="C23" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E23">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -2119,16 +2086,16 @@
         <v>20</v>
       </c>
       <c r="C24" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E24">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2139,16 +2106,16 @@
         <v>20</v>
       </c>
       <c r="C25" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E25">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F25" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -2159,16 +2126,16 @@
         <v>20</v>
       </c>
       <c r="C26" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E26">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -2179,16 +2146,16 @@
         <v>20</v>
       </c>
       <c r="C27" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E27">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -2199,16 +2166,16 @@
         <v>20</v>
       </c>
       <c r="C28" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E28">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -2219,16 +2186,16 @@
         <v>20</v>
       </c>
       <c r="C29" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E29">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -2239,16 +2206,16 @@
         <v>20</v>
       </c>
       <c r="C30" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E30">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -2259,16 +2226,16 @@
         <v>20</v>
       </c>
       <c r="C31" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F31" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -2279,16 +2246,16 @@
         <v>20</v>
       </c>
       <c r="C32" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E32">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -2299,16 +2266,16 @@
         <v>20</v>
       </c>
       <c r="C33" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E33">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -2319,16 +2286,16 @@
         <v>20</v>
       </c>
       <c r="C34" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E34">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F34" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -2339,16 +2306,16 @@
         <v>20</v>
       </c>
       <c r="C35" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E35">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2359,16 +2326,16 @@
         <v>20</v>
       </c>
       <c r="C36" t="s">
-        <v>69</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>49</v>
+        <v>66</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="E36">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F36" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2379,16 +2346,16 @@
         <v>20</v>
       </c>
       <c r="C37" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E37">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F37" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -2399,16 +2366,16 @@
         <v>20</v>
       </c>
       <c r="C38" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E38">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F38" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2419,16 +2386,16 @@
         <v>20</v>
       </c>
       <c r="C39" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E39">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F39" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -2439,16 +2406,16 @@
         <v>20</v>
       </c>
       <c r="C40" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E40">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F40" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -2459,16 +2426,16 @@
         <v>20</v>
       </c>
       <c r="C41" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E41">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F41" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2479,16 +2446,16 @@
         <v>20</v>
       </c>
       <c r="C42" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E42">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2499,16 +2466,16 @@
         <v>20</v>
       </c>
       <c r="C43" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E43">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F43" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2519,16 +2486,16 @@
         <v>20</v>
       </c>
       <c r="C44" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E44">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F44" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2539,16 +2506,16 @@
         <v>20</v>
       </c>
       <c r="C45" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E45">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F45" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2559,16 +2526,16 @@
         <v>20</v>
       </c>
       <c r="C46" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E46">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F46" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2579,16 +2546,16 @@
         <v>20</v>
       </c>
       <c r="C47" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E47">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F47" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2599,16 +2566,16 @@
         <v>20</v>
       </c>
       <c r="C48" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E48">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F48" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2619,16 +2586,16 @@
         <v>20</v>
       </c>
       <c r="C49" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E49">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F49" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2639,16 +2606,16 @@
         <v>20</v>
       </c>
       <c r="C50" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E50">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -2659,16 +2626,16 @@
         <v>20</v>
       </c>
       <c r="C51" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E51">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F51" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -2679,16 +2646,16 @@
         <v>20</v>
       </c>
       <c r="C52" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E52">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F52" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -2699,16 +2666,16 @@
         <v>20</v>
       </c>
       <c r="C53" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E53">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F53" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -2719,16 +2686,16 @@
         <v>20</v>
       </c>
       <c r="C54" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E54">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F54" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -2739,16 +2706,16 @@
         <v>20</v>
       </c>
       <c r="C55" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E55">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F55" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -2759,16 +2726,16 @@
         <v>20</v>
       </c>
       <c r="C56" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E56">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F56" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -2779,16 +2746,16 @@
         <v>20</v>
       </c>
       <c r="C57" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E57">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F57" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -2799,16 +2766,16 @@
         <v>20</v>
       </c>
       <c r="C58" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E58">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F58" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -2819,16 +2786,16 @@
         <v>20</v>
       </c>
       <c r="C59" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E59">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F59" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2839,16 +2806,16 @@
         <v>20</v>
       </c>
       <c r="C60" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E60">
         <v>7</v>
       </c>
       <c r="F60" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2859,16 +2826,16 @@
         <v>20</v>
       </c>
       <c r="C61" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E61">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F61" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -2879,16 +2846,16 @@
         <v>20</v>
       </c>
       <c r="C62" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E62">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F62" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -2899,16 +2866,16 @@
         <v>20</v>
       </c>
       <c r="C63" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E63">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F63" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -2919,16 +2886,16 @@
         <v>20</v>
       </c>
       <c r="C64" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E64">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F64" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2939,16 +2906,16 @@
         <v>20</v>
       </c>
       <c r="C65" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E65">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F65" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -2959,16 +2926,16 @@
         <v>20</v>
       </c>
       <c r="C66" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E66">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F66" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -2979,16 +2946,16 @@
         <v>20</v>
       </c>
       <c r="C67" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E67">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F67" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -2999,16 +2966,16 @@
         <v>20</v>
       </c>
       <c r="C68" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E68">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F68" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -3019,16 +2986,16 @@
         <v>20</v>
       </c>
       <c r="C69" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E69">
         <v>6</v>
       </c>
       <c r="F69" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -3039,16 +3006,16 @@
         <v>20</v>
       </c>
       <c r="C70" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E70">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F70" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -3059,16 +3026,16 @@
         <v>20</v>
       </c>
       <c r="C71" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E71">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F71" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -3079,16 +3046,16 @@
         <v>20</v>
       </c>
       <c r="C72" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E72">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F72" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -3099,16 +3066,16 @@
         <v>20</v>
       </c>
       <c r="C73" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E73">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="F73" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -3119,16 +3086,16 @@
         <v>20</v>
       </c>
       <c r="C74" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E74">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="F74" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -3139,16 +3106,16 @@
         <v>20</v>
       </c>
       <c r="C75" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E75">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F75" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -3159,16 +3126,16 @@
         <v>20</v>
       </c>
       <c r="C76" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E76">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F76" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -3179,16 +3146,16 @@
         <v>20</v>
       </c>
       <c r="C77" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E77">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F77" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -3199,16 +3166,16 @@
         <v>20</v>
       </c>
       <c r="C78" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E78">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F78" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -3219,16 +3186,16 @@
         <v>20</v>
       </c>
       <c r="C79" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E79">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F79" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -3239,16 +3206,16 @@
         <v>20</v>
       </c>
       <c r="C80" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E80">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F80" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -3259,16 +3226,16 @@
         <v>20</v>
       </c>
       <c r="C81" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E81">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F81" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3279,16 +3246,16 @@
         <v>20</v>
       </c>
       <c r="C82" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E82">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F82" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3299,16 +3266,16 @@
         <v>20</v>
       </c>
       <c r="C83" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E83">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F83" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -3319,16 +3286,16 @@
         <v>20</v>
       </c>
       <c r="C84" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E84">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F84" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -3339,16 +3306,16 @@
         <v>20</v>
       </c>
       <c r="C85" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E85">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F85" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -3359,16 +3326,16 @@
         <v>20</v>
       </c>
       <c r="C86" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E86">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F86" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -3379,16 +3346,16 @@
         <v>20</v>
       </c>
       <c r="C87" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E87">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F87" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3399,16 +3366,16 @@
         <v>20</v>
       </c>
       <c r="C88" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E88">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F88" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3419,16 +3386,16 @@
         <v>20</v>
       </c>
       <c r="C89" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E89">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F89" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -3439,16 +3406,16 @@
         <v>20</v>
       </c>
       <c r="C90" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E90">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F90" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -3459,16 +3426,16 @@
         <v>20</v>
       </c>
       <c r="C91" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E91">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F91" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3479,16 +3446,16 @@
         <v>20</v>
       </c>
       <c r="C92" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E92">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F92" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3499,16 +3466,16 @@
         <v>20</v>
       </c>
       <c r="C93" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E93">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F93" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -3519,16 +3486,16 @@
         <v>20</v>
       </c>
       <c r="C94" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E94">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F94" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3539,16 +3506,16 @@
         <v>20</v>
       </c>
       <c r="C95" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E95">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F95" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3559,16 +3526,16 @@
         <v>20</v>
       </c>
       <c r="C96" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E96">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F96" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3579,16 +3546,16 @@
         <v>20</v>
       </c>
       <c r="C97" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E97">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F97" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3599,16 +3566,16 @@
         <v>20</v>
       </c>
       <c r="C98" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E98">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F98" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3619,16 +3586,16 @@
         <v>20</v>
       </c>
       <c r="C99" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E99">
         <v>7</v>
       </c>
       <c r="F99" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3639,16 +3606,16 @@
         <v>20</v>
       </c>
       <c r="C100" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E100">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F100" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3659,16 +3626,16 @@
         <v>20</v>
       </c>
       <c r="C101" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E101">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F101" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3679,16 +3646,16 @@
         <v>22</v>
       </c>
       <c r="C102" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E102">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F102" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -3699,16 +3666,16 @@
         <v>22</v>
       </c>
       <c r="C103" t="s">
-        <v>137</v>
-      </c>
-      <c r="D103" s="4" t="s">
-        <v>49</v>
+        <v>133</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="E103">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F103" t="s">
-        <v>138</v>
+        <v>32</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -3719,16 +3686,16 @@
         <v>22</v>
       </c>
       <c r="C104" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E104">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="F104" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -3739,16 +3706,16 @@
         <v>22</v>
       </c>
       <c r="C105" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E105">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F105" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3759,16 +3726,16 @@
         <v>22</v>
       </c>
       <c r="C106" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E106">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F106" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3779,16 +3746,16 @@
         <v>22</v>
       </c>
       <c r="C107" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E107">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F107" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3799,16 +3766,16 @@
         <v>22</v>
       </c>
       <c r="C108" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E108">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F108" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3819,16 +3786,16 @@
         <v>22</v>
       </c>
       <c r="C109" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E109">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F109" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3839,16 +3806,16 @@
         <v>22</v>
       </c>
       <c r="C110" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E110">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F110" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -3859,16 +3826,16 @@
         <v>22</v>
       </c>
       <c r="C111" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E111">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F111" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -3879,16 +3846,16 @@
         <v>22</v>
       </c>
       <c r="C112" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E112">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F112" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -3899,16 +3866,16 @@
         <v>22</v>
       </c>
       <c r="C113" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E113">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F113" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -3919,16 +3886,16 @@
         <v>22</v>
       </c>
       <c r="C114" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E114">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F114" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3939,16 +3906,16 @@
         <v>22</v>
       </c>
       <c r="C115" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E115">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F115" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -3959,16 +3926,16 @@
         <v>22</v>
       </c>
       <c r="C116" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E116">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F116" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -3979,16 +3946,16 @@
         <v>22</v>
       </c>
       <c r="C117" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E117">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F117" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -3999,16 +3966,16 @@
         <v>22</v>
       </c>
       <c r="C118" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E118">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F118" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -4019,16 +3986,16 @@
         <v>22</v>
       </c>
       <c r="C119" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E119">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F119" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -4039,16 +4006,16 @@
         <v>22</v>
       </c>
       <c r="C120" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E120">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F120" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -4059,16 +4026,16 @@
         <v>22</v>
       </c>
       <c r="C121" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E121">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F121" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -4079,16 +4046,16 @@
         <v>22</v>
       </c>
       <c r="C122" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E122">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F122" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -4099,16 +4066,16 @@
         <v>22</v>
       </c>
       <c r="C123" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E123">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F123" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -4119,16 +4086,16 @@
         <v>22</v>
       </c>
       <c r="C124" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E124">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F124" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -4139,16 +4106,16 @@
         <v>22</v>
       </c>
       <c r="C125" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E125">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F125" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -4159,16 +4126,16 @@
         <v>22</v>
       </c>
       <c r="C126" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E126">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F126" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -4179,16 +4146,16 @@
         <v>22</v>
       </c>
       <c r="C127" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E127">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="F127" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -4199,16 +4166,16 @@
         <v>22</v>
       </c>
       <c r="C128" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E128">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F128" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -4219,16 +4186,16 @@
         <v>22</v>
       </c>
       <c r="C129" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E129">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F129" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4239,16 +4206,16 @@
         <v>22</v>
       </c>
       <c r="C130" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E130">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F130" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4259,16 +4226,16 @@
         <v>22</v>
       </c>
       <c r="C131" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E131">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F131" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -4279,16 +4246,16 @@
         <v>22</v>
       </c>
       <c r="C132" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E132">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F132" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4299,16 +4266,16 @@
         <v>22</v>
       </c>
       <c r="C133" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E133">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F133" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4319,16 +4286,16 @@
         <v>22</v>
       </c>
       <c r="C134" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E134">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F134" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4339,16 +4306,16 @@
         <v>22</v>
       </c>
       <c r="C135" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E135">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F135" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4359,16 +4326,16 @@
         <v>22</v>
       </c>
       <c r="C136" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E136">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="F136" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -4379,16 +4346,16 @@
         <v>22</v>
       </c>
       <c r="C137" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E137">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F137" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -4399,16 +4366,16 @@
         <v>22</v>
       </c>
       <c r="C138" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E138">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F138" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -4419,16 +4386,16 @@
         <v>22</v>
       </c>
       <c r="C139" t="s">
-        <v>174</v>
-      </c>
-      <c r="D139" s="4" t="s">
-        <v>49</v>
+        <v>169</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="E139">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F139" t="s">
-        <v>175</v>
+        <v>32</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -4439,16 +4406,16 @@
         <v>22</v>
       </c>
       <c r="C140" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E140">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F140" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -4459,16 +4426,16 @@
         <v>22</v>
       </c>
       <c r="C141" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E141">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F141" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -4479,16 +4446,16 @@
         <v>22</v>
       </c>
       <c r="C142" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E142">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F142" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -4499,16 +4466,16 @@
         <v>22</v>
       </c>
       <c r="C143" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E143">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F143" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4519,16 +4486,16 @@
         <v>22</v>
       </c>
       <c r="C144" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E144">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F144" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -4539,16 +4506,16 @@
         <v>22</v>
       </c>
       <c r="C145" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E145">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F145" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -4559,16 +4526,16 @@
         <v>22</v>
       </c>
       <c r="C146" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E146">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F146" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -4579,16 +4546,16 @@
         <v>22</v>
       </c>
       <c r="C147" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E147">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F147" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -4599,16 +4566,16 @@
         <v>22</v>
       </c>
       <c r="C148" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E148">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F148" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -4619,16 +4586,16 @@
         <v>22</v>
       </c>
       <c r="C149" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E149">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F149" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -4639,16 +4606,16 @@
         <v>22</v>
       </c>
       <c r="C150" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E150">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F150" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -4659,16 +4626,16 @@
         <v>22</v>
       </c>
       <c r="C151" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E151">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F151" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -4679,16 +4646,16 @@
         <v>22</v>
       </c>
       <c r="C152" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E152">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F152" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -4699,16 +4666,16 @@
         <v>22</v>
       </c>
       <c r="C153" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E153">
         <v>10</v>
       </c>
       <c r="F153" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -4719,16 +4686,16 @@
         <v>22</v>
       </c>
       <c r="C154" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E154">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="F154" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -4739,16 +4706,16 @@
         <v>22</v>
       </c>
       <c r="C155" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E155">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F155" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -4759,16 +4726,16 @@
         <v>22</v>
       </c>
       <c r="C156" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E156">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F156" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -4779,16 +4746,16 @@
         <v>22</v>
       </c>
       <c r="C157" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E157">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F157" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -4799,16 +4766,16 @@
         <v>22</v>
       </c>
       <c r="C158" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E158">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F158" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -4819,16 +4786,16 @@
         <v>22</v>
       </c>
       <c r="C159" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E159">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F159" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -4839,16 +4806,16 @@
         <v>22</v>
       </c>
       <c r="C160" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E160">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F160" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -4859,16 +4826,16 @@
         <v>22</v>
       </c>
       <c r="C161" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E161">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="F161" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -4879,16 +4846,16 @@
         <v>22</v>
       </c>
       <c r="C162" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E162">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F162" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -4899,16 +4866,16 @@
         <v>22</v>
       </c>
       <c r="C163" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E163">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F163" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -4919,16 +4886,16 @@
         <v>22</v>
       </c>
       <c r="C164" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E164">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F164" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -4939,16 +4906,16 @@
         <v>22</v>
       </c>
       <c r="C165" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E165">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F165" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -4959,16 +4926,16 @@
         <v>22</v>
       </c>
       <c r="C166" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E166">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F166" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -4979,16 +4946,16 @@
         <v>22</v>
       </c>
       <c r="C167" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E167">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F167" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -4999,16 +4966,16 @@
         <v>22</v>
       </c>
       <c r="C168" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E168">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F168" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -5019,16 +4986,16 @@
         <v>22</v>
       </c>
       <c r="C169" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E169">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F169" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -5039,16 +5006,16 @@
         <v>22</v>
       </c>
       <c r="C170" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E170">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F170" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -5059,16 +5026,16 @@
         <v>22</v>
       </c>
       <c r="C171" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E171">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F171" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -5079,16 +5046,16 @@
         <v>22</v>
       </c>
       <c r="C172" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E172">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F172" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -5099,16 +5066,16 @@
         <v>22</v>
       </c>
       <c r="C173" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E173">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F173" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -5119,16 +5086,16 @@
         <v>22</v>
       </c>
       <c r="C174" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E174">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F174" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -5139,16 +5106,16 @@
         <v>22</v>
       </c>
       <c r="C175" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E175">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F175" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -5159,16 +5126,16 @@
         <v>22</v>
       </c>
       <c r="C176" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E176">
         <v>18</v>
       </c>
       <c r="F176" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -5179,16 +5146,16 @@
         <v>22</v>
       </c>
       <c r="C177" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E177">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F177" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -5199,16 +5166,16 @@
         <v>22</v>
       </c>
       <c r="C178" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E178">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F178" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -5219,16 +5186,16 @@
         <v>22</v>
       </c>
       <c r="C179" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E179">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="F179" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -5239,16 +5206,16 @@
         <v>22</v>
       </c>
       <c r="C180" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E180">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F180" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -5259,16 +5226,16 @@
         <v>22</v>
       </c>
       <c r="C181" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E181">
         <v>8</v>
       </c>
       <c r="F181" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -5279,16 +5246,16 @@
         <v>22</v>
       </c>
       <c r="C182" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E182">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F182" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -5299,16 +5266,16 @@
         <v>22</v>
       </c>
       <c r="C183" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E183">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F183" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -5319,16 +5286,16 @@
         <v>22</v>
       </c>
       <c r="C184" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E184">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F184" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -5339,16 +5306,16 @@
         <v>22</v>
       </c>
       <c r="C185" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E185">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F185" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -5359,16 +5326,16 @@
         <v>22</v>
       </c>
       <c r="C186" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E186">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F186" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -5379,16 +5346,16 @@
         <v>22</v>
       </c>
       <c r="C187" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E187">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F187" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -5399,16 +5366,16 @@
         <v>22</v>
       </c>
       <c r="C188" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E188">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F188" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -5419,16 +5386,16 @@
         <v>22</v>
       </c>
       <c r="C189" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E189">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F189" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -5439,16 +5406,16 @@
         <v>22</v>
       </c>
       <c r="C190" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E190">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F190" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -5459,16 +5426,16 @@
         <v>22</v>
       </c>
       <c r="C191" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E191">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F191" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -5479,16 +5446,16 @@
         <v>22</v>
       </c>
       <c r="C192" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E192">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F192" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -5499,16 +5466,16 @@
         <v>22</v>
       </c>
       <c r="C193" t="s">
-        <v>229</v>
-      </c>
-      <c r="D193" s="4" t="s">
-        <v>49</v>
+        <v>223</v>
+      </c>
+      <c r="D193" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="E193">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="F193" t="s">
-        <v>230</v>
+        <v>32</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -5519,16 +5486,16 @@
         <v>22</v>
       </c>
       <c r="C194" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E194">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F194" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -5539,16 +5506,16 @@
         <v>22</v>
       </c>
       <c r="C195" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E195">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F195" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -5559,16 +5526,16 @@
         <v>22</v>
       </c>
       <c r="C196" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E196">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F196" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -5579,16 +5546,16 @@
         <v>22</v>
       </c>
       <c r="C197" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E197">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F197" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -5599,16 +5566,16 @@
         <v>22</v>
       </c>
       <c r="C198" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E198">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F198" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -5619,16 +5586,16 @@
         <v>22</v>
       </c>
       <c r="C199" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E199">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F199" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -5639,16 +5606,16 @@
         <v>22</v>
       </c>
       <c r="C200" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E200">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F200" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -5659,16 +5626,16 @@
         <v>22</v>
       </c>
       <c r="C201" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E201">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F201" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -5676,19 +5643,19 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C202" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E202">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F202" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -5696,19 +5663,19 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C203" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E203">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F203" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -5716,19 +5683,19 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C204" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E204">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F204" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -5736,19 +5703,19 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C205" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E205">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F205" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -5756,19 +5723,19 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C206" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E206">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F206" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -5776,19 +5743,19 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C207" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E207">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F207" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
@@ -5796,19 +5763,19 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C208" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E208">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F208" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
@@ -5816,19 +5783,19 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C209" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E209">
         <v>6</v>
       </c>
       <c r="F209" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
@@ -5836,19 +5803,19 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C210" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E210">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F210" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -5856,19 +5823,19 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C211" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E211">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F211" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -5876,19 +5843,19 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C212" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E212">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F212" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -5896,19 +5863,19 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C213" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E213">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F213" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -5916,19 +5883,19 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C214" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E214">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F214" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -5936,19 +5903,19 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C215" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E215">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F215" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -5956,19 +5923,19 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C216" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E216">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F216" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -5976,19 +5943,19 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C217" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E217">
         <v>10</v>
       </c>
       <c r="F217" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
@@ -5996,19 +5963,19 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C218" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E218">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F218" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -6016,19 +5983,19 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C219" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E219">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F219" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -6036,19 +6003,19 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C220" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E220">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F220" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -6056,19 +6023,19 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C221" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E221">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F221" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -6076,19 +6043,19 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E222">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F222" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -6096,19 +6063,19 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C223" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E223">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F223" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -6116,19 +6083,19 @@
         <v>223</v>
       </c>
       <c r="B224" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C224" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E224">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F224" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -6136,19 +6103,19 @@
         <v>224</v>
       </c>
       <c r="B225" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C225" t="s">
-        <v>262</v>
-      </c>
-      <c r="D225" s="4" t="s">
-        <v>49</v>
+        <v>255</v>
+      </c>
+      <c r="D225" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="E225">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F225" t="s">
-        <v>263</v>
+        <v>32</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -6156,19 +6123,19 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C226" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E226">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F226" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -6176,19 +6143,19 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C227" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="D227" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E227">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F227" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -6196,19 +6163,19 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C228" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E228">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="F228" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -6216,19 +6183,19 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C229" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E229">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F229" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -6236,19 +6203,19 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C230" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E230">
         <v>7</v>
       </c>
       <c r="F230" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
@@ -6256,19 +6223,19 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C231" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E231">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F231" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -6276,19 +6243,19 @@
         <v>231</v>
       </c>
       <c r="B232" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C232" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E232">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F232" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -6296,19 +6263,19 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C233" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E233">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F233" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
@@ -6316,19 +6283,19 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C234" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E234">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F234" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
@@ -6336,19 +6303,19 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C235" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E235">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F235" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
@@ -6356,19 +6323,19 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C236" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E236">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F236" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
@@ -6376,19 +6343,19 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C237" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E237">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F237" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
@@ -6396,19 +6363,19 @@
         <v>237</v>
       </c>
       <c r="B238" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C238" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E238">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F238" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
@@ -6416,19 +6383,19 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C239" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E239">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F239" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
@@ -6436,19 +6403,19 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C240" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E240">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F240" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -6456,19 +6423,19 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C241" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E241">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F241" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -6476,19 +6443,19 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C242" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E242">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F242" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
@@ -6496,19 +6463,19 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C243" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E243">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F243" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
@@ -6516,19 +6483,19 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C244" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E244">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F244" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -6536,19 +6503,19 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C245" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="D245" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E245">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F245" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
@@ -6556,19 +6523,19 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C246" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="D246" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E246">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F246" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
@@ -6576,19 +6543,19 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C247" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E247">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F247" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
@@ -6596,19 +6563,19 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C248" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="D248" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E248">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F248" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
@@ -6616,19 +6583,19 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C249" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="D249" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E249">
         <v>19</v>
       </c>
       <c r="F249" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -6636,19 +6603,19 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C250" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E250">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F250" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -6656,19 +6623,19 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C251" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="D251" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E251">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F251" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -6676,19 +6643,19 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C252" t="s">
-        <v>290</v>
-      </c>
-      <c r="D252" s="4" t="s">
-        <v>49</v>
+        <v>282</v>
+      </c>
+      <c r="D252" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="E252">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F252" t="s">
-        <v>291</v>
+        <v>32</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -6696,19 +6663,19 @@
         <v>252</v>
       </c>
       <c r="B253" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C253" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E253">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F253" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -6716,19 +6683,19 @@
         <v>253</v>
       </c>
       <c r="B254" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C254" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="D254" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E254">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="F254" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
@@ -6736,19 +6703,19 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C255" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="D255" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E255">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F255" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -6756,19 +6723,19 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C256" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="D256" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E256">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F256" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
@@ -6776,19 +6743,19 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C257" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="D257" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E257">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F257" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -6796,19 +6763,19 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C258" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="D258" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E258">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F258" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -6816,19 +6783,19 @@
         <v>258</v>
       </c>
       <c r="B259" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C259" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="D259" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E259">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F259" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -6836,19 +6803,19 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C260" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="D260" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E260">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F260" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
@@ -6856,19 +6823,19 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C261" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="D261" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E261">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F261" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -6876,19 +6843,19 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C262" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="D262" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E262">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F262" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
@@ -6896,19 +6863,19 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C263" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="D263" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E263">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F263" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -6916,19 +6883,19 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C264" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="D264" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E264">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F264" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
@@ -6936,19 +6903,19 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C265" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="D265" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E265">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F265" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
@@ -6956,19 +6923,19 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C266" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="D266" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E266">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F266" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
@@ -6976,19 +6943,19 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C267" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="D267" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E267">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F267" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
@@ -6996,19 +6963,19 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C268" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="D268" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E268">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F268" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
@@ -7016,19 +6983,19 @@
         <v>268</v>
       </c>
       <c r="B269" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C269" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="D269" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E269">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F269" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
@@ -7036,19 +7003,19 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C270" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="D270" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E270">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F270" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
@@ -7056,19 +7023,19 @@
         <v>270</v>
       </c>
       <c r="B271" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C271" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="D271" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E271">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F271" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
@@ -7076,19 +7043,19 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C272" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="D272" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E272">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F272" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
@@ -7096,19 +7063,19 @@
         <v>272</v>
       </c>
       <c r="B273" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C273" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="D273" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E273">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F273" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
@@ -7116,19 +7083,19 @@
         <v>273</v>
       </c>
       <c r="B274" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C274" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="D274" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E274">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F274" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
@@ -7136,19 +7103,19 @@
         <v>274</v>
       </c>
       <c r="B275" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C275" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E275">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F275" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
@@ -7156,19 +7123,19 @@
         <v>275</v>
       </c>
       <c r="B276" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C276" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="D276" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E276">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F276" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
@@ -7176,19 +7143,19 @@
         <v>276</v>
       </c>
       <c r="B277" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C277" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="D277" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E277">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F277" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
@@ -7196,19 +7163,19 @@
         <v>277</v>
       </c>
       <c r="B278" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C278" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="D278" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E278">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F278" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
@@ -7216,19 +7183,19 @@
         <v>278</v>
       </c>
       <c r="B279" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C279" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="D279" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E279">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F279" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
@@ -7236,19 +7203,19 @@
         <v>279</v>
       </c>
       <c r="B280" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C280" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="D280" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E280">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F280" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
@@ -7256,19 +7223,19 @@
         <v>280</v>
       </c>
       <c r="B281" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C281" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="D281" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E281">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F281" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
@@ -7276,19 +7243,19 @@
         <v>281</v>
       </c>
       <c r="B282" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C282" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="D282" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E282">
         <v>14</v>
       </c>
       <c r="F282" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
@@ -7296,19 +7263,19 @@
         <v>282</v>
       </c>
       <c r="B283" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C283" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="D283" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E283">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F283" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
@@ -7316,19 +7283,19 @@
         <v>283</v>
       </c>
       <c r="B284" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C284" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="D284" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E284">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="F284" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
@@ -7336,19 +7303,19 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C285" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="D285" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E285">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F285" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
@@ -7356,19 +7323,19 @@
         <v>285</v>
       </c>
       <c r="B286" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C286" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="D286" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E286">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F286" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
@@ -7376,19 +7343,19 @@
         <v>286</v>
       </c>
       <c r="B287" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C287" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="D287" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E287">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="F287" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
@@ -7396,19 +7363,19 @@
         <v>287</v>
       </c>
       <c r="B288" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C288" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="D288" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E288">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F288" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -7416,19 +7383,19 @@
         <v>288</v>
       </c>
       <c r="B289" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C289" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="D289" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E289">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F289" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
@@ -7436,19 +7403,19 @@
         <v>289</v>
       </c>
       <c r="B290" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C290" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="D290" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E290">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F290" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -7456,19 +7423,19 @@
         <v>290</v>
       </c>
       <c r="B291" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C291" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="D291" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E291">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F291" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
@@ -7476,19 +7443,19 @@
         <v>291</v>
       </c>
       <c r="B292" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C292" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="D292" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E292">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F292" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -7496,19 +7463,19 @@
         <v>292</v>
       </c>
       <c r="B293" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C293" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="D293" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E293">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F293" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -7516,19 +7483,19 @@
         <v>293</v>
       </c>
       <c r="B294" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C294" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="D294" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E294">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F294" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -7536,19 +7503,19 @@
         <v>294</v>
       </c>
       <c r="B295" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C295" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="D295" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E295">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F295" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -7556,19 +7523,19 @@
         <v>295</v>
       </c>
       <c r="B296" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C296" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="D296" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E296">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F296" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -7576,19 +7543,19 @@
         <v>296</v>
       </c>
       <c r="B297" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C297" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="D297" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E297">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F297" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -7596,19 +7563,19 @@
         <v>297</v>
       </c>
       <c r="B298" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C298" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="D298" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E298">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F298" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -7616,19 +7583,19 @@
         <v>298</v>
       </c>
       <c r="B299" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C299" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="D299" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E299">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F299" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -7636,19 +7603,19 @@
         <v>299</v>
       </c>
       <c r="B300" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C300" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="D300" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E300">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F300" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
@@ -7656,19 +7623,19 @@
         <v>300</v>
       </c>
       <c r="B301" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C301" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="D301" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E301">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F301" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
